--- a/Benchmark.xlsx
+++ b/Benchmark.xlsx
@@ -574,261 +574,271 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <f>AVERAGE(D9,D15,D21)</f>
+        <v>2.861079999</v>
+      </c>
+      <c r="F22" s="3">
+        <f>AVERAGE(F9,F15,F21)</f>
+        <v>2.932929473</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B24" s="2">
         <v>0.41493</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C24" s="2">
         <v>1.558504</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E24" s="2">
         <v>1.789141</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="2">
-        <v>0.486538</v>
-      </c>
-      <c r="C24" s="2">
-        <v>1.847149</v>
-      </c>
-      <c r="E24" s="2">
-        <v>1.626946</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="2">
-        <v>0.406146</v>
+        <v>0.486538</v>
       </c>
       <c r="C25" s="2">
-        <v>1.50734</v>
+        <v>1.847149</v>
       </c>
       <c r="E25" s="2">
-        <v>1.608884</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>9</v>
+        <v>1.626946</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="2">
-        <v>0.406708</v>
+        <v>0.406146</v>
       </c>
       <c r="C26" s="2">
-        <v>1.51113</v>
+        <v>1.50734</v>
       </c>
       <c r="E26" s="2">
-        <v>1.591559</v>
+        <v>1.608884</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="2">
+        <v>0.406708</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1.51113</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1.591559</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2">
         <v>0.399013</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C28" s="2">
         <v>1.51171</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E28" s="2">
         <v>1.599102</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="3">
-        <f t="shared" ref="B28:C28" si="4">AVERAGE(B23:B27)</f>
+    <row r="29">
+      <c r="B29" s="3">
+        <f t="shared" ref="B29:C29" si="4">AVERAGE(B24:B28)</f>
         <v>0.422667</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C29" s="3">
         <f t="shared" si="4"/>
         <v>1.5871666</v>
       </c>
-      <c r="D28" s="3">
-        <f>C28/B28</f>
+      <c r="D29" s="3">
+        <f>C29/B29</f>
         <v>3.755123064</v>
       </c>
-      <c r="E28" s="3">
-        <f>AVERAGE(E23:E27)</f>
+      <c r="E29" s="3">
+        <f>AVERAGE(E24:E28)</f>
         <v>1.6431264</v>
       </c>
-      <c r="F28" s="3">
-        <f>E28/B28</f>
+      <c r="F29" s="3">
+        <f>E29/B29</f>
         <v>3.887519963</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="s">
+    <row r="30">
+      <c r="A30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B30" s="2">
         <v>1.683318</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C30" s="2">
         <v>6.246025</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E30" s="2">
         <v>6.393328</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="2">
-        <v>1.692611</v>
-      </c>
-      <c r="C30" s="2">
-        <v>6.052342</v>
-      </c>
-      <c r="E30" s="2">
-        <v>6.351642</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="2">
-        <v>1.688085</v>
+        <v>1.692611</v>
       </c>
       <c r="C31" s="2">
-        <v>5.981858</v>
+        <v>6.052342</v>
       </c>
       <c r="E31" s="2">
-        <v>6.619294</v>
+        <v>6.351642</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="2">
-        <v>1.697486</v>
+        <v>1.688085</v>
       </c>
       <c r="C32" s="2">
-        <v>6.234638</v>
+        <v>5.981858</v>
       </c>
       <c r="E32" s="2">
-        <v>6.466189</v>
+        <v>6.619294</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="2">
+        <v>1.697486</v>
+      </c>
+      <c r="C33" s="2">
+        <v>6.234638</v>
+      </c>
+      <c r="E33" s="2">
+        <v>6.466189</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="2">
         <v>1.696381</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C34" s="2">
         <v>6.326127</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E34" s="2">
         <v>6.710412</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="3">
-        <f t="shared" ref="B34:C34" si="5">AVERAGE(B29:B33)</f>
+    <row r="35">
+      <c r="B35" s="3">
+        <f t="shared" ref="B35:C35" si="5">AVERAGE(B30:B34)</f>
         <v>1.6915762</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C35" s="3">
         <f t="shared" si="5"/>
         <v>6.168198</v>
       </c>
-      <c r="D34" s="3">
-        <f>C34/B34</f>
+      <c r="D35" s="3">
+        <f>C35/B35</f>
         <v>3.646420421</v>
       </c>
-      <c r="E34" s="3">
-        <f>AVERAGE(E29:E33)</f>
+      <c r="E35" s="3">
+        <f>AVERAGE(E30:E34)</f>
         <v>6.508173</v>
       </c>
-      <c r="F34" s="3">
-        <f>E34/B34</f>
+      <c r="F35" s="3">
+        <f>E35/B35</f>
         <v>3.847401613</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="s">
+    <row r="36">
+      <c r="A36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B36" s="2">
         <v>9.845941</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C36" s="2">
         <v>42.313626</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E36" s="2">
         <v>44.907436</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="2">
-        <v>10.581197</v>
-      </c>
-      <c r="C36" s="2">
-        <v>43.748352</v>
-      </c>
-      <c r="E36" s="2">
-        <v>47.644988</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="2">
-        <v>10.224846</v>
+        <v>10.581197</v>
       </c>
       <c r="C37" s="2">
-        <v>42.84662</v>
+        <v>43.748352</v>
       </c>
       <c r="E37" s="2">
-        <v>46.472489</v>
+        <v>47.644988</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="2">
-        <v>10.280666</v>
+        <v>10.224846</v>
       </c>
       <c r="C38" s="2">
-        <v>43.082782</v>
+        <v>42.84662</v>
       </c>
       <c r="E38" s="2">
-        <v>48.180568</v>
+        <v>46.472489</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="2">
+        <v>10.280666</v>
+      </c>
+      <c r="C39" s="2">
+        <v>43.082782</v>
+      </c>
+      <c r="E39" s="2">
+        <v>48.180568</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="2">
         <v>9.686459</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C40" s="2">
         <v>40.495029</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E40" s="2">
         <v>48.012366</v>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="3">
-        <f t="shared" ref="B40:C40" si="6">AVERAGE(B35:B39)</f>
+    <row r="41">
+      <c r="B41" s="3">
+        <f t="shared" ref="B41:C41" si="6">AVERAGE(B36:B40)</f>
         <v>10.1238218</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C41" s="3">
         <f t="shared" si="6"/>
         <v>42.4972818</v>
       </c>
-      <c r="D40" s="3">
-        <f>C40/B40</f>
+      <c r="D41" s="3">
+        <f>C41/B41</f>
         <v>4.197750873</v>
       </c>
-      <c r="E40" s="3">
-        <f>AVERAGE(E35:E39)</f>
+      <c r="E41" s="3">
+        <f>AVERAGE(E36:E40)</f>
         <v>47.0435694</v>
       </c>
-      <c r="F40" s="3">
-        <f>E40/B40</f>
+      <c r="F41" s="3">
+        <f>E41/B41</f>
         <v>4.646819188</v>
       </c>
     </row>
     <row r="42">
       <c r="D42" s="3">
-        <f>AVERAGE(D9,D15,D21,D28,D34,D40)</f>
-        <v>3.363755726</v>
+        <f>AVERAGE(D29,D35,D41)</f>
+        <v>3.866431453</v>
       </c>
       <c r="F42" s="3">
-        <f>AVERAGE(F9,F15,F21,F28,F34,F40)</f>
-        <v>3.530088197</v>
+        <f>AVERAGE(F29,F35,F41)</f>
+        <v>4.127246921</v>
       </c>
     </row>
   </sheetData>
